--- a/public/sample_leads_template.xlsx
+++ b/public/sample_leads_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,43 +409,103 @@
       <c r="C1" t="str">
         <v>Email</v>
       </c>
+      <c r="D1" t="str">
+        <v>Address Line 1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Address Line 2</v>
+      </c>
+      <c r="F1" t="str">
+        <v>City</v>
+      </c>
+      <c r="G1" t="str">
+        <v>State</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Zip Code</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Demo User India</v>
+        <v>Ronald E Wilcox</v>
       </c>
       <c r="B2" t="str">
-        <v>+919876500001</v>
+        <v>+16027692922</v>
       </c>
       <c r="C2" t="str">
-        <v>demo.india@example.com</v>
+        <v>ronwilcox@cox.net</v>
+      </c>
+      <c r="D2" t="str">
+        <v>120 W ALMERIA RD</v>
+      </c>
+      <c r="E2" t="str">
+        <v>120 W ALMERIA RD PHOENIX AZ 85003-1139</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="G2" t="str">
+        <v>AZ</v>
+      </c>
+      <c r="H2" t="str">
+        <v>85003-1139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Demo User USA</v>
+        <v>Keith A Watson</v>
       </c>
       <c r="B3" t="str">
-        <v>+14155500002</v>
+        <v>+18139184214</v>
       </c>
       <c r="C3" t="str">
-        <v>demo.usa@example.com</v>
+        <v>keithwatsonsr@gmail.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>4135 N RIVER DRIVE</v>
+      </c>
+      <c r="E3" t="str">
+        <v>4135 N RIVER DRIVE EDEN UT 84310</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Eden</v>
+      </c>
+      <c r="G3" t="str">
+        <v>UT</v>
+      </c>
+      <c r="H3" t="str">
+        <v>84310</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Demo User UK</v>
+        <v>Hector Julian</v>
       </c>
       <c r="B4" t="str">
-        <v>+447911000003</v>
+        <v>+13472511962</v>
       </c>
       <c r="C4" t="str">
-        <v>demo.uk@example.com</v>
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>209 W 40TH ST # 7AVE</v>
+      </c>
+      <c r="E4" t="str">
+        <v>209 W 40TH ST # 7AVE NEW YORK NY 10018</v>
+      </c>
+      <c r="F4" t="str">
+        <v>New York</v>
+      </c>
+      <c r="G4" t="str">
+        <v>NY</v>
+      </c>
+      <c r="H4" t="str">
+        <v>10018</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/sample_leads_template.xlsx
+++ b/public/sample_leads_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Leads" sheetId="1" r:id="rId1"/>
+    <sheet name="Leads_Template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K4"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,6 +437,15 @@
       <c r="H1" t="str">
         <v>Zip Code</v>
       </c>
+      <c r="I1" t="str">
+        <v>Product</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Price</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -439,7 +461,7 @@
         <v>120 W ALMERIA RD</v>
       </c>
       <c r="E2" t="str">
-        <v>120 W ALMERIA RD PHOENIX AZ 85003-1139</v>
+        <v>Suite 100</v>
       </c>
       <c r="F2" t="str">
         <v>Phoenix</v>
@@ -449,63 +471,90 @@
       </c>
       <c r="H2" t="str">
         <v>85003-1139</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Cenforce 100mg</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Keith A Watson</v>
+        <v>John Smith</v>
       </c>
       <c r="B3" t="str">
-        <v>+18139184214</v>
+        <v>+14155552671</v>
       </c>
       <c r="C3" t="str">
-        <v>keithwatsonsr@gmail.com</v>
+        <v>john.smith@example.com</v>
       </c>
       <c r="D3" t="str">
-        <v>4135 N RIVER DRIVE</v>
+        <v>742 Evergreen Terrace</v>
       </c>
       <c r="E3" t="str">
-        <v>4135 N RIVER DRIVE EDEN UT 84310</v>
+        <v>Apt 4B</v>
       </c>
       <c r="F3" t="str">
-        <v>Eden</v>
+        <v>Springfield</v>
       </c>
       <c r="G3" t="str">
-        <v>UT</v>
+        <v>OR</v>
       </c>
       <c r="H3" t="str">
-        <v>84310</v>
+        <v>97477</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Modafinil 200mg</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Hector Julian</v>
+        <v>David Wilson</v>
       </c>
       <c r="B4" t="str">
-        <v>+13472511962</v>
+        <v>+447911123456</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>david.wilson@example.co.uk</v>
       </c>
       <c r="D4" t="str">
-        <v>209 W 40TH ST # 7AVE</v>
+        <v>10 Downing Street</v>
       </c>
       <c r="E4" t="str">
-        <v>209 W 40TH ST # 7AVE NEW YORK NY 10018</v>
+        <v>Westminster</v>
       </c>
       <c r="F4" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="G4" t="str">
-        <v>NY</v>
+        <v>Greater London</v>
       </c>
       <c r="H4" t="str">
-        <v>10018</v>
+        <v>SW1A 2AA</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Kamagra Oral Jelly</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>